--- a/howling-way-スプレッドシートひな型.xlsx
+++ b/howling-way-スプレッドシートひな型.xlsx
@@ -1195,20 +1195,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>【作品】CD・配信作品の情報を入力すると、サイトのDiscographyに表示されます。上から順（新しい順がおすすめ）に表示されます。</t>
+          <t>【作品】CD・配信作品の情報を入力すると、サイトのDiscographyに表示されます。上から順（新しい順がおすすめ）に表示されます。「概要」を入力すると、作品詳細ページのリリース情報とTRACKLISTの間に誌明文が表示されます（空樓でも可）。</t>
         </is>
       </c>
     </row>
@@ -1235,6 +1236,11 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>公開</t>
         </is>
       </c>
@@ -1262,6 +1268,11 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>概要</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>公開</t>
         </is>
       </c>
@@ -1289,6 +1300,11 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
+          <t>Howling way 2作目となるミニアルバム。過去最多の全7曲を収録し、バンドの新たな一面を切り押いた作品。</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
           <t>TRUE</t>
         </is>
       </c>
@@ -1314,7 +1330,7 @@
           <t>beautiful</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1341,7 +1357,7 @@
           <t>ラストラリー / HEART</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1368,7 +1384,7 @@
           <t>ギフト / 人の子のため / いつかすべてを / スーツ / スーパーヒーロー / 遠吠え / 未完成ライダー</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1376,10 +1392,10 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="E4:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F4:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
